--- a/daily_matches/job_matches_2026-08-29.xlsx
+++ b/daily_matches/job_matches_2026-08-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,165 +468,165 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Associate, Senior Engineer - Institutional Life Technology</t>
+          <t>Backend Senior Software Engineer, CX Engineering(Hybrid)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, S3, Glue, Redshift, CI/CD, Terraform, Redshift</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, NoSQL, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68fedabc5fbe0a42</t>
+          <t>https://www.indeed.com/viewjob?jk=119b27074f6796ab</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Science &amp; Advanced Analytics</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>East West Bank</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MongoDB, NoSQL</t>
+          <t>Generative AI, RAG, Copilot, TensorFlow, PyTorch, XGBoost, Azure ML, MLflow, CI/CD, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38d8d179e35c0ba3</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4ddfbb836aef9f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Continental Resources, Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Prompt Engineering, Docker, CI/CD, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0384a05edc9e1207</t>
+          <t>https://www.indeed.com/viewjob?jk=086ab9a12df1ee39</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Calfus</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MySQL</t>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Kafka, MongoDB, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86e62449c4c85c8e</t>
+          <t>https://www.indeed.com/viewjob?jk=27c60023bc663d82</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Products</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Focus on the Family</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Cortex, CI/CD, Git, Snowflake, Tableau, Power BI, Python, SQL</t>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Kafka, MongoDB, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b735c1f0f9c927f</t>
+          <t>https://www.indeed.com/viewjob?jk=4484d09ea245cffb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist IV - Risk Adjustment: Medicare, Medicaid, ACA</t>
+          <t>Software Development Engineer 2 (Java 17+)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kaiser Permanente</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, AKS, Python, SQL, R, Scala, Optimization</t>
+          <t>EC2, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,77 +671,532 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a0eabb8100ebea2</t>
+          <t>https://www.indeed.com/viewjob?jk=fb5406d04d45cf36</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Engineer – Managed IT Services (5117)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SMX</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, S3, Glue, Redshift, Data Lake, CI/CD, Git, Snowflake, Redshift, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18154d374ffc0b0c</t>
+          <t>https://www.indeed.com/viewjob?jk=ad211ca6801fd529</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SERVAL</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Redshift, Data Lake, CI/CD, Git, Snowflake, Redshift, SQL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd833b3f3ca71894</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Koch</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Redshift, Data Lake, CI/CD, Git, Snowflake, Redshift, SQL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc966b8e4ac5ea90</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Customer Operations Data Analyst</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mimecast</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Lexington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbce3cba9ad623c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Field Specialist - Data Engineering &amp; Streaming (Pre-Sales)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cloudera</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Glue, Dataflow, Kubernetes, CI/CD, Git, Databricks, Kafka, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf2e066f006a0c05</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Software</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>WM</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, EC2, FastAPI, Docker, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92dbce536ddead5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior QA Engineer, Austin TX</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SailPoint Technologies</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, S3, Kubernetes, CI/CD, Snowflake, Databricks, Kafka, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34cf8dcd205d0971</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sr Applied Data Scientist - Personalization (applied ML, PyTorch, ML Ops)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Brooklyn Park, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7632b49d68fa3277</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sr AI Engineer - Advanced AI (ML Ops, LLMs, Agentic workflows)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Brooklyn Park, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, LLaMA, TensorFlow, PyTorch, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64c3655ac7c56d8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>API Platform Owner</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Axos Bank</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=875223ae2058a7a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Engineer, Subscriptions DevOps</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>The Washington Post</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, CI/CD, Jenkins, Terraform, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e74ffa7c8423e777</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>GenAI Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=451964c7217bbbce</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Xylem</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>10</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, Terraform, Snowflake, Databricks, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80eefb0800d23658</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AI Practitioner</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ITA Group Inc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>West Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=78bbf5b38558f11e</t>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17cc7945bc0203ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Engineer - Finance AI Solutions</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Brooklyn Park, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, PySpark, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a64225cf49e7ac0e</t>
         </is>
       </c>
     </row>
